--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-healthcareservice-implementation-period.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="127">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-implementation-period</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-implementation-period</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -335,30 +335,11 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>Extension.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.id</t>
-  </si>
-  <si>
     <t>Extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.extension</t>
   </si>
   <si>
     <t>Extension.value[x].extension</t>
@@ -377,9 +358,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Extension.value[x]:valuePeriod.start</t>
-  </si>
-  <si>
     <t>Extension.value[x].start</t>
   </si>
   <si>
@@ -407,9 +385,6 @@
   </si>
   <si>
     <t>./low</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.end</t>
   </si>
   <si>
     <t>Extension.value[x].end</t>
@@ -732,10 +707,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1373,14 +1348,16 @@
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AC6" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>100</v>
@@ -1395,7 +1372,7 @@
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>99</v>
@@ -1403,14 +1380,12 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
@@ -1431,13 +1406,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1488,7 +1463,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1497,32 +1472,32 @@
         <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1534,15 +1509,17 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>74</v>
@@ -1579,34 +1556,34 @@
         <v>74</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1614,18 +1591,18 @@
         <v>111</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1634,10 +1611,10 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>114</v>
@@ -1684,42 +1661,42 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1739,10 +1716,10 @@
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>121</v>
@@ -1757,7 +1734,9 @@
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q10" s="2"/>
+      <c r="Q10" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="R10" t="s" s="2">
         <v>74</v>
       </c>
@@ -1801,7 +1780,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -1810,120 +1789,13 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>126</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="R11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
